--- a/output/pdf_financials_xlsx/HC.xlsx
+++ b/output/pdf_financials_xlsx/HC.xlsx
@@ -1474,16 +1474,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.221579</v>
+        <v>0.004646</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.050422</v>
+        <v>0.375998</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.347243</v>
+        <v>1.206147</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.77595</v>
+        <v>0.7425349999999999</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>1.1289</v>
@@ -2454,19 +2454,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.09346</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.8388099999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.690546</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.425322</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.947093</v>
       </c>
     </row>
     <row r="93">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -4334,7 +4334,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -4369,7 +4373,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -5065,7 +5073,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -5098,7 +5110,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5207,7 +5223,11 @@
           <t>Warrants reserve 12</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -5783,7 +5803,11 @@
           <t>Warrants reserve 13</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
         <v>0.047484</v>
       </c>
@@ -5818,7 +5842,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>0.045976</v>
       </c>

--- a/output/pdf_financials_xlsx/HC.xlsx
+++ b/output/pdf_financials_xlsx/HC.xlsx
@@ -1474,16 +1474,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.004646</v>
+        <v>0.221579</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.375998</v>
+        <v>6.050422</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.206147</v>
+        <v>1.347243</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.7425349999999999</v>
+        <v>0.77595</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>1.1289</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">

--- a/output/pdf_financials_xlsx/HC.xlsx
+++ b/output/pdf_financials_xlsx/HC.xlsx
@@ -1301,16 +1301,16 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.044951</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.02044</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.229025</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.04637</v>
       </c>
     </row>
     <row r="41">
@@ -1323,16 +1323,16 @@
         <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.499811</v>
+        <v>0.544762</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.82506</v>
+        <v>0.8455</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.464562</v>
+        <v>1.693587</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.567449</v>
+        <v>2.613819</v>
       </c>
     </row>
     <row r="42">
@@ -1477,16 +1477,16 @@
         <v>0.221579</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.050422</v>
+        <v>6.005471</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.347243</v>
+        <v>1.326803</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.77595</v>
+        <v>0.546925</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.1289</v>
+        <v>1.08253</v>
       </c>
     </row>
     <row r="49">
@@ -1911,10 +1911,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.590369</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.509251</v>
       </c>
     </row>
     <row r="68">
@@ -2681,19 +2681,19 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.004646</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.369597</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.830149</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.463908</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.46088</v>
       </c>
     </row>
     <row r="104">
@@ -2747,19 +2747,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.202187</v>
+        <v>0.197541</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.693968</v>
+        <v>-1.063565</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.330649</v>
+        <v>-0.4995</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.219586</v>
+        <v>0.683494</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1.606061</v>
+        <v>1.145181</v>
       </c>
     </row>
     <row r="107">
@@ -2857,19 +2857,19 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002698</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.157811</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.03835</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.188537</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.085273</v>
       </c>
     </row>
     <row r="112">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002698</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.157811</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.03835</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.188537</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.085273</v>
       </c>
     </row>
     <row r="135">
@@ -3399,19 +3399,19 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.383711</v>
+        <v>-0.386409</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-4.574186</v>
+        <v>-4.731997</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.746082</v>
+        <v>-3.784432</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-5.341374</v>
+        <v>-5.529911</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.346552</v>
+        <v>-2.431825</v>
       </c>
     </row>
   </sheetData>
@@ -6277,7 +6277,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>-0.004646</v>
       </c>
@@ -6462,7 +6466,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -7350,7 +7358,11 @@
           <t>Purchase of equipment 9</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E99" s="5" t="n">
         <v>-0.002698</v>
       </c>
